--- a/Employee_Reports_wi52/Lorence Cardenas Cabales Q0614.xlsx
+++ b/Employee_Reports_wi52/Lorence Cardenas Cabales Q0614.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,6 +84,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -560,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1148,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1197,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1246,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1283,11 +1292,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1332,11 +1341,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1381,11 +1390,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1431,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1480,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1517,11 +1526,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1554,11 +1563,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1603,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1652,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1701,11 +1710,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1750,11 +1759,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1787,11 +1796,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1824,11 +1833,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1861,11 +1870,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1898,11 +1907,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1935,11 +1944,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -1984,11 +1993,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -1997,6 +2006,43 @@
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2012,15 +2058,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
     <col width="2" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2158,52 +2204,83 @@
       <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Logimat</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>56.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>low percentage</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Bin Transport System</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>29-Apr-2026</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>perfect score</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Congratulations on achieving a perfect score!!!! date is valid</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>93.28%</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>85.83%</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2291,7 +2368,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7808</v>
+        <v>7800</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
